--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486699_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486699_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7177</v>
+        <v>4.2958</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1703</v>
+        <v>3.5498</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5474</v>
+        <v>0.746</v>
       </c>
       <c r="G2" t="n">
         <v>2.0848</v>
@@ -610,13 +610,13 @@
         <v>1.1585</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1803</v>
+        <v>0.7584</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1858</v>
+        <v>0.5652</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0055</v>
+        <v>0.1932</v>
       </c>
       <c r="V2" t="n">
         <v>0.2941</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. DIAZ FELST</t>
+          <t>P. GRIMA LORENZO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.7379</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4355</v>
+        <v>0.2078</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3024</v>
+        <v>-1.1377</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.1461</v>
+        <v>1.358</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1243</v>
+        <v>3.7589</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.0218</v>
+        <v>-2.4008</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006</v>
+        <v>3.5939</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0828</v>
+        <v>4.9322</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-1.3383</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1521</v>
+        <v>-2.2359</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2071</v>
+        <v>-1.1733</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.945</v>
+        <v>-1.0626</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3862</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3515</v>
+        <v>1.9308</v>
       </c>
       <c r="S3" t="n">
-        <v>0.022</v>
+        <v>-0.1034</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5239</v>
+        <v>-0.4899</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5019</v>
+        <v>0.3866</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-1.2192</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.2192</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. GRIMA LORENZO</t>
+          <t>M. DIAZ FELST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.3891</v>
+        <v>-0.9737</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1025</v>
+        <v>-0.7458</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2867</v>
+        <v>-0.2279</v>
       </c>
       <c r="G4" t="n">
-        <v>1.358</v>
+        <v>-1.1461</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7589</v>
+        <v>-0.1243</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.4008</v>
+        <v>-1.0218</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5939</v>
+        <v>0.006</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9322</v>
+        <v>0.0828</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.3383</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.2359</v>
+        <v>-1.1521</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1733</v>
+        <v>-0.2071</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0626</v>
+        <v>-0.945</v>
       </c>
       <c r="P4" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="Q4" t="n">
         <v>-0.9654</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-2.8962</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.9308</v>
+        <v>1.3515</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5626</v>
+        <v>-0.2138</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8002</v>
+        <v>0.2137</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2376</v>
+        <v>-0.4274</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2192</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. GONZALEZ-MONJE PEREZ</t>
+          <t>J. PARRONDO CASTRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.552</v>
+        <v>-1.1917</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7374000000000001</v>
+        <v>-0.5985</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.2894</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.5943</v>
+        <v>-0.8227</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1791</v>
+        <v>0.111</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4152</v>
+        <v>-0.9337</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9859</v>
+        <v>2.0273</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0627</v>
+        <v>1.9052</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.1221</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5802</v>
+        <v>-2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2418</v>
+        <v>-1.7942</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3384</v>
+        <v>-1.0558</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3169</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.8616</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3169</v>
+        <v>3.0892</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1986</v>
+        <v>0.1518</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2485</v>
+        <v>-0.235</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0499</v>
+        <v>0.3867</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.076</v>
+        <v>0.2515</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.4707</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.076</v>
+        <v>-1.2192</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. PARRONDO CASTRO</t>
+          <t>M. GONZALEZ-MONJE PEREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7129</v>
+        <v>-1.2706</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2191</v>
+        <v>0.9443</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4939</v>
+        <v>-2.2149</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8227</v>
+        <v>-1.5943</v>
       </c>
       <c r="H6" t="n">
-        <v>0.111</v>
+        <v>-0.1791</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9337</v>
+        <v>-1.4152</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0273</v>
+        <v>0.9859</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9052</v>
+        <v>1.0627</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1221</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.85</v>
+        <v>-2.5802</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.7942</v>
+        <v>-1.2418</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0558</v>
+        <v>-1.3384</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7723</v>
+        <v>2.3169</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.8616</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.0892</v>
+        <v>2.3169</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3694</v>
+        <v>0.0827</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8555</v>
+        <v>-0.0417</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4861</v>
+        <v>0.1244</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2515</v>
+        <v>-2.076</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4707</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2192</v>
+        <v>-2.076</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9628</v>
+        <v>-2.4551</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2199</v>
+        <v>1.7028</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.1827</v>
+        <v>-4.1579</v>
       </c>
       <c r="G7" t="n">
         <v>-3.0077</v>
@@ -1000,13 +1000,13 @@
         <v>0.3862</v>
       </c>
       <c r="S7" t="n">
-        <v>1.23</v>
+        <v>0.7377</v>
       </c>
       <c r="T7" t="n">
-        <v>1.627</v>
+        <v>1.1099</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.397</v>
+        <v>-0.3722</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5712</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.7174</v>
+        <v>-2.4597</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3593</v>
+        <v>-0.3251</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.358</v>
+        <v>-2.1346</v>
       </c>
       <c r="G8" t="n">
         <v>-2.0761</v>
@@ -1078,13 +1078,13 @@
         <v>0.5792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9268999999999999</v>
+        <v>0.3308</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6622</v>
+        <v>0.372</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2647</v>
+        <v>-0.0412</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3282</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. VIVANCOS ORTIZ</t>
+          <t>A. GOMEZ PEÑA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.5983</v>
+        <v>-4.1767</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4043</v>
+        <v>-4.5187</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.194</v>
+        <v>0.342</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.2421</v>
+        <v>-1.8368</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5655</v>
+        <v>1.0613</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.6766</v>
+        <v>-2.8981</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.6619</v>
+        <v>1.0753</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3237</v>
+        <v>2.6486</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3383</v>
+        <v>-1.5733</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.5802</v>
+        <v>-2.9121</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2418</v>
+        <v>-1.5873</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3384</v>
+        <v>-1.3248</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-2.51</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9654</v>
+        <v>-5.7923</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9654</v>
+        <v>3.2823</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8715000000000001</v>
+        <v>-0.124</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9374</v>
+        <v>-0.3729</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0659</v>
+        <v>0.2489</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2277</v>
+        <v>0.2941</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2856</v>
+        <v>0.5712</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5133</v>
+        <v>-0.2771</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6123</v>
+        <v>-4.3517</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5169</v>
+        <v>-2.2066</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0954</v>
+        <v>-2.1451</v>
       </c>
       <c r="G10" t="n">
         <v>-3.9448</v>
@@ -1234,13 +1234,13 @@
         <v>0.3862</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0883</v>
+        <v>0.1723</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4963</v>
+        <v>0.8065</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5846</v>
+        <v>-0.6342</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. GOMEZ PEÑA</t>
+          <t>E. VIVANCOS ORTIZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6979</v>
+        <v>-4.801</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.1392</v>
+        <v>-1.5077</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4413</v>
+        <v>-3.2933</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8368</v>
+        <v>-4.2421</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0613</v>
+        <v>-1.5655</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.8981</v>
+        <v>-2.6766</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0753</v>
+        <v>-1.6619</v>
       </c>
       <c r="K11" t="n">
-        <v>2.6486</v>
+        <v>-0.3237</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5733</v>
+        <v>-1.3383</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.9121</v>
+        <v>-2.5802</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5873</v>
+        <v>-1.2418</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3248</v>
+        <v>-1.3384</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.51</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.7923</v>
+        <v>-0.9654</v>
       </c>
       <c r="R11" t="n">
-        <v>3.2823</v>
+        <v>0.9654</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6452</v>
+        <v>0.6688</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9933999999999999</v>
+        <v>0.834</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3482</v>
+        <v>-0.1652</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2941</v>
+        <v>-1.2277</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5712</v>
+        <v>0.2856</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2771</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.519299999999999</v>
+        <v>-11.4679</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.1845</v>
+        <v>-8.735799999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3348</v>
+        <v>-2.7321</v>
       </c>
       <c r="G12" t="n">
         <v>-8.943899999999999</v>
@@ -1390,13 +1390,13 @@
         <v>1.9308</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9346</v>
+        <v>0.986</v>
       </c>
       <c r="T12" t="n">
-        <v>2.7851</v>
+        <v>1.2338</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1495</v>
+        <v>-0.2478</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6138</v>
@@ -1426,10 +1426,10 @@
         <v>-29.7822</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.2337</v>
+        <v>-12.2335</v>
       </c>
       <c r="F13" t="n">
-        <v>-17.5486</v>
+        <v>-17.5487</v>
       </c>
       <c r="G13" t="n">
         <v>-24.1717</v>
@@ -1468,13 +1468,13 @@
         <v>17.377</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4474</v>
+        <v>3.4473</v>
       </c>
       <c r="T13" t="n">
-        <v>3.9957</v>
+        <v>3.9956</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5483</v>
+        <v>-0.5482</v>
       </c>
       <c r="V13" t="n">
         <v>-5.196400000000001</v>
@@ -1483,7 +1483,7 @@
         <v>4.412</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.608499999999999</v>
+        <v>-9.608500000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.392</v>
+        <v>6.4388</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9106</v>
+        <v>5.6345</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4815</v>
+        <v>0.8043</v>
       </c>
       <c r="G14" t="n">
         <v>5.9646</v>
@@ -1546,13 +1546,13 @@
         <v>1.7377</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.7157</v>
+        <v>-0.6689000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8277</v>
+        <v>-0.1038</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.888</v>
+        <v>-0.5651</v>
       </c>
       <c r="V14" t="n">
         <v>0.3709</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. SANCHEZ PARRA</t>
+          <t>G. CAMPOS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4731</v>
+        <v>4.8145</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9692</v>
+        <v>3.677</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5039</v>
+        <v>1.1376</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1106</v>
+        <v>3.0184</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8206</v>
+        <v>1.8067</v>
       </c>
       <c r="I15" t="n">
-        <v>2.29</v>
+        <v>1.2117</v>
       </c>
       <c r="J15" t="n">
-        <v>2.215</v>
+        <v>1.9777</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4418</v>
+        <v>1.3243</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7732</v>
+        <v>0.6534</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8956</v>
+        <v>1.0408</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6212</v>
+        <v>0.4824</v>
       </c>
       <c r="O15" t="n">
-        <v>1.5169</v>
+        <v>0.5583</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1239</v>
+        <v>0.7723</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1239</v>
+        <v>0.7723</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1381</v>
+        <v>-0.4895</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0825</v>
+        <v>0.186</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0556</v>
+        <v>-0.6755</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.8995</v>
+        <v>1.5133</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3282</v>
+        <v>1.5133</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. CAMPOS RODRIGUEZ</t>
+          <t>S. SANCHEZ PARRA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3719</v>
+        <v>4.5558</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1599</v>
+        <v>1.7624</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2121</v>
+        <v>2.7934</v>
       </c>
       <c r="G16" t="n">
-        <v>3.0184</v>
+        <v>3.1106</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8067</v>
+        <v>0.8206</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2117</v>
+        <v>2.29</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9777</v>
+        <v>2.215</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3243</v>
+        <v>1.4418</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6534</v>
+        <v>0.7732</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0408</v>
+        <v>0.8956</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4824</v>
+        <v>-0.6212</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5583</v>
+        <v>1.5169</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7723</v>
+        <v>2.1239</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7723</v>
+        <v>2.1239</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9321</v>
+        <v>0.2208</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3311</v>
+        <v>-0.1244</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.601</v>
+        <v>0.3451</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5133</v>
+        <v>-0.8995</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5133</v>
+        <v>-0.3282</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.375</v>
+        <v>3.8135</v>
       </c>
       <c r="E17" t="n">
         <v>1.8078</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5672</v>
+        <v>2.0057</v>
       </c>
       <c r="G17" t="n">
         <v>3.136</v>
@@ -1780,13 +1780,13 @@
         <v>2.51</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2317</v>
+        <v>0.2068</v>
       </c>
       <c r="T17" t="n">
         <v>-0.2486</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0169</v>
+        <v>0.4554</v>
       </c>
       <c r="V17" t="n">
         <v>0.8568</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. GARCIA GARCIA</t>
+          <t>J. ORAMAS MARTEL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.3307</v>
+        <v>2.9554</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1081</v>
+        <v>1.7659</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2226</v>
+        <v>1.1895</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1878</v>
+        <v>2.3446</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3864</v>
+        <v>-0.531</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5742</v>
+        <v>2.8756</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9973</v>
+        <v>2.8142</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5927</v>
+        <v>0.3658</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4046</v>
+        <v>2.4484</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1851</v>
+        <v>-0.4697</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2063</v>
+        <v>-0.8969</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9788</v>
+        <v>0.4272</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1239</v>
+        <v>1.7377</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6988</v>
+        <v>0.1241</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7852</v>
+        <v>-0.083</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0864</v>
+        <v>0.2071</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2856</v>
+        <v>-0.2856</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.6041</v>
+        <v>2.5915</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3127</v>
+        <v>2.6229</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2914</v>
+        <v>-0.0314</v>
       </c>
       <c r="G19" t="n">
         <v>5.4631</v>
@@ -1936,13 +1936,13 @@
         <v>1.9308</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3804</v>
+        <v>-0.3929</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0279</v>
+        <v>0.2824</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3525</v>
+        <v>-0.6753</v>
       </c>
       <c r="V19" t="n">
         <v>-1.5133</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. ORAMAS MARTEL</t>
+          <t>J. GONZÁLEZ CHÁVEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.1417</v>
+        <v>2.2467</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3522</v>
+        <v>0.6131</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7895</v>
+        <v>1.6336</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3446</v>
+        <v>0.1028</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.531</v>
+        <v>0.2068</v>
       </c>
       <c r="I20" t="n">
-        <v>2.8756</v>
+        <v>-0.104</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8142</v>
+        <v>-0.5236</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3658</v>
+        <v>0.6903</v>
       </c>
       <c r="L20" t="n">
-        <v>2.4484</v>
+        <v>-1.2139</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4697</v>
+        <v>0.6264</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8969</v>
+        <v>-0.4835</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4272</v>
+        <v>1.1099</v>
       </c>
       <c r="P20" t="n">
         <v>0.7723</v>
@@ -2014,28 +2014,28 @@
         <v>1.7377</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6895</v>
+        <v>-1.0411</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4966</v>
+        <v>-0.3106</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1929</v>
+        <v>-0.7305</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2856</v>
+        <v>2.4128</v>
       </c>
       <c r="W20" t="n">
+        <v>2.4128</v>
+      </c>
+      <c r="X20" t="n">
         <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-0.2856</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. GONZÁLEZ CHÁVEZ</t>
+          <t>J. GARCIA CABRERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4787</v>
+        <v>2.0122</v>
       </c>
       <c r="E21" t="n">
-        <v>0.096</v>
+        <v>0.2336</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3827</v>
+        <v>1.7786</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1028</v>
+        <v>0.9291</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2068</v>
+        <v>0.572</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.104</v>
+        <v>0.3572</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5236</v>
+        <v>0.2403</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6903</v>
+        <v>0.8484</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2139</v>
+        <v>-0.6081</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6264</v>
+        <v>0.6889</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4835</v>
+        <v>-0.2764</v>
       </c>
       <c r="O21" t="n">
-        <v>1.1099</v>
+        <v>0.9653</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7723</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7377</v>
+        <v>1.5446</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.8092</v>
+        <v>-0.3723</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8277</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9815</v>
+        <v>-0.4549</v>
       </c>
       <c r="V21" t="n">
-        <v>2.4128</v>
+        <v>1.8415</v>
       </c>
       <c r="W21" t="n">
-        <v>2.4128</v>
+        <v>1.8415</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. GANDARA MARTIN</t>
+          <t>J. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.3495</v>
+        <v>1.7353</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0126</v>
+        <v>-0.65</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3621</v>
+        <v>2.3853</v>
       </c>
       <c r="G22" t="n">
-        <v>2.563</v>
+        <v>0.1878</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1379</v>
+        <v>-0.3864</v>
       </c>
       <c r="I22" t="n">
-        <v>0.425</v>
+        <v>0.5742</v>
       </c>
       <c r="J22" t="n">
-        <v>3.3153</v>
+        <v>-0.9973</v>
       </c>
       <c r="K22" t="n">
-        <v>3.3108</v>
+        <v>-0.5927</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0046</v>
+        <v>-0.4046</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7524</v>
+        <v>1.1851</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1728</v>
+        <v>0.2063</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4205</v>
+        <v>0.9788</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.3169</v>
+        <v>1.1585</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.8616</v>
+        <v>-0.9654</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5446</v>
+        <v>2.1239</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1035</v>
+        <v>0.1034</v>
       </c>
       <c r="T22" t="n">
-        <v>0.248</v>
+        <v>1.027</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8554</v>
+        <v>-0.9236</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="W22" t="n">
         <v>0.2856</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. GARCIA CABRERA</t>
+          <t>M. MOLINA HERRERA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2371</v>
+        <v>1.5586</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1801</v>
+        <v>0.8867</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4172</v>
+        <v>0.672</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9291</v>
+        <v>-0.7034</v>
       </c>
       <c r="H23" t="n">
-        <v>0.572</v>
+        <v>-0.6966</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3572</v>
+        <v>-0.0068</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2403</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8484</v>
+        <v>1.3731</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6081</v>
+        <v>-0.5651</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6889</v>
+        <v>-1.5113</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2764</v>
+        <v>-2.0697</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9653</v>
+        <v>0.5583</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3862</v>
+        <v>1.1585</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5446</v>
+        <v>2.1239</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1474</v>
+        <v>-0.1242</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3311</v>
+        <v>-0.4692</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8163</v>
+        <v>0.3451</v>
       </c>
       <c r="V23" t="n">
-        <v>1.8415</v>
+        <v>1.2277</v>
       </c>
       <c r="W23" t="n">
-        <v>1.8415</v>
+        <v>1.5133</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. MOLINA HERRERA</t>
+          <t>E. GANDARA MARTIN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8829</v>
+        <v>0.8046</v>
       </c>
       <c r="E24" t="n">
-        <v>0.473</v>
+        <v>-0.3229</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4099</v>
+        <v>1.1275</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7034</v>
+        <v>2.563</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6966</v>
+        <v>2.1379</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0068</v>
+        <v>0.425</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8080000000000001</v>
+        <v>3.3153</v>
       </c>
       <c r="K24" t="n">
-        <v>1.3731</v>
+        <v>3.3108</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5651</v>
+        <v>0.0046</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5113</v>
+        <v>-0.7524</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.0697</v>
+        <v>-1.1728</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5583</v>
+        <v>0.4205</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1585</v>
+        <v>-2.3169</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9654</v>
+        <v>-3.8616</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1239</v>
+        <v>1.5446</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7999000000000001</v>
+        <v>0.5586</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8829</v>
+        <v>-0.0622</v>
       </c>
       <c r="U24" t="n">
-        <v>0.083</v>
+        <v>0.6209</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.5133</v>
+        <v>0.2856</v>
       </c>
       <c r="X24" t="n">
         <v>-0.2856</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.8545</v>
+        <v>-1.6764</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5518999999999999</v>
+        <v>-0.4823</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4064</v>
+        <v>-1.194</v>
       </c>
       <c r="G25" t="n">
         <v>-1.945</v>
@@ -2404,13 +2404,13 @@
         <v>1.3515</v>
       </c>
       <c r="S25" t="n">
-        <v>1.3181</v>
+        <v>0.4963</v>
       </c>
       <c r="T25" t="n">
-        <v>1.4063</v>
+        <v>0.372</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0881</v>
+        <v>0.1243</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6138</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>29.7822</v>
+        <v>31.8505</v>
       </c>
       <c r="E26" t="n">
         <v>17.5487</v>
       </c>
       <c r="F26" t="n">
-        <v>12.2337</v>
+        <v>14.3021</v>
       </c>
       <c r="G26" t="n">
         <v>24.1716</v>
       </c>
       <c r="H26" t="n">
-        <v>2.4127</v>
+        <v>2.412699999999999</v>
       </c>
       <c r="I26" t="n">
         <v>21.7588</v>
@@ -2482,13 +2482,13 @@
         <v>21.2386</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.447399999999999</v>
+        <v>-1.3789</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5484000000000004</v>
+        <v>0.5481999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.9958</v>
+        <v>-1.927</v>
       </c>
       <c r="V26" t="n">
         <v>5.1964</v>
